--- a/artfynd/A 18094-2026 artfynd.xlsx
+++ b/artfynd/A 18094-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129370734</v>
+        <v>129381012</v>
       </c>
       <c r="B2" t="n">
-        <v>96000</v>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420110</v>
+        <v>420160</v>
       </c>
       <c r="R2" t="n">
-        <v>6612672</v>
+        <v>6612183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tämligen klen låga i 50 årig granskog. Rotticka på samma låga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129380255</v>
+        <v>129381285</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420173</v>
+        <v>420112</v>
       </c>
       <c r="R3" t="n">
-        <v>6612254</v>
+        <v>6612211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129381012</v>
+        <v>129370734</v>
       </c>
       <c r="B4" t="n">
-        <v>92288</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420160</v>
+        <v>420110</v>
       </c>
       <c r="R4" t="n">
-        <v>6612183</v>
+        <v>6612672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,17 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tämligen klen låga i 50 årig granskog. Rotticka på samma låga.</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129381285</v>
+        <v>129380255</v>
       </c>
       <c r="B5" t="n">
-        <v>92247</v>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420112</v>
+        <v>420173</v>
       </c>
       <c r="R5" t="n">
-        <v>6612211</v>
+        <v>6612254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 18094-2026 artfynd.xlsx
+++ b/artfynd/A 18094-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129381012</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129381285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129370734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129380255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>